--- a/data/trans_orig/IP31B_R_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31B_R_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35748</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27558</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>45234</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29,49%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,74%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>37,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>25667</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18753</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33736</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>25,44%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44095</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34170</t>
+          <t>18757</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58574</t>
+          <t>32866</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>69762</t>
+          <t>61041</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57764</t>
+          <t>50803</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85997</t>
+          <t>73126</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>85461</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>75975</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>93651</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>70,51%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>62,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,26%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>75211</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>67142</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>74,56%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>66,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91081</t>
+          <t>74338</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76602</t>
+          <t>66765</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101006</t>
+          <t>80874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>166292</t>
+          <t>159800</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150057</t>
+          <t>147715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>178290</t>
+          <t>170038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>100878</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>100878</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>100878</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>99631</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>99631</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>99631</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236054</t>
+          <t>220841</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236054</t>
+          <t>220841</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236054</t>
+          <t>220841</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22143</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15783</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29688</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>33,03%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>28600</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>21636</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>36425</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>30,62%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>28779</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>22109</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>36482</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>30,16%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>23,17%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>39,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>24134</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>17402</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>31614</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>25,75%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>18,57%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>52735</t>
+          <t>50922</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43173</t>
+          <t>40851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63568</t>
+          <t>61366</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>67737</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60192</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>74097</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>75,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>66,97%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>82,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>64792</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>56967</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>71756</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>69,38%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>61,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>66631</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>58928</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>73301</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>69,84%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>61,76%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>76,83%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>69574</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>62094</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>76306</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>74,25%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>66,26%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>81,43%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>186</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>134366</t>
+          <t>134368</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>123533</t>
+          <t>123924</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143928</t>
+          <t>144439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17545</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12197</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23540</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21,84%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42,15%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>15239</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10399</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22334</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21536</t>
+          <t>16019</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15511</t>
+          <t>10535</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>23258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>36775</t>
+          <t>33564</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28270</t>
+          <t>24604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46681</t>
+          <t>41366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>38299</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>32304</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43647</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>68,58%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>57,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>78,16%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>34850</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>27755</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>39690</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>69,58%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>55,41%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>79,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40798</t>
+          <t>35991</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32752</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46823</t>
+          <t>41475</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>75647</t>
+          <t>74290</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65741</t>
+          <t>66488</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84152</t>
+          <t>83250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>77,19%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>79749</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>67080</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>95242</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>40,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>34,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>48,64%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>98934</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>76384</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>136380</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>46,31%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35,75%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>63,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>88786</t>
+          <t>64365</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74517</t>
+          <t>54165</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104122</t>
+          <t>75168</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>187720</t>
+          <t>144115</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163359</t>
+          <t>126680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>238682</t>
+          <t>160758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>43,38%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>116044</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>100551</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>128713</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>59,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>51,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>65,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>114707</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>77261</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>137257</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>53,69%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>36,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>64,25%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>122334</t>
+          <t>110391</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106998</t>
+          <t>99588</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136603</t>
+          <t>120591</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>237041</t>
+          <t>226435</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>186079</t>
+          <t>209792</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261402</t>
+          <t>243870</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>195793</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>195793</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>195793</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>213641</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>213641</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>213641</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>211120</t>
+          <t>174756</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>211120</t>
+          <t>174756</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>211120</t>
+          <t>174756</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>424761</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>424761</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>424761</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>44277</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33979</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>54468</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30,9%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>23,72%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>38,02%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>33220</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>25918</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>41777</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>28,76%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>36,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>50127</t>
+          <t>31757</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37935</t>
+          <t>24054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62372</t>
+          <t>39765</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>83347</t>
+          <t>76034</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69302</t>
+          <t>62820</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97021</t>
+          <t>88702</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>98993</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>88802</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>109291</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>69,1%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>61,98%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>76,28%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>82289</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>73732</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>89591</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>71,24%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>63,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>77,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>105691</t>
+          <t>83709</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93446</t>
+          <t>75701</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117883</t>
+          <t>91412</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>187980</t>
+          <t>182702</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>174306</t>
+          <t>170034</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>202025</t>
+          <t>195916</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>75,72%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143270</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143270</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143270</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>155818</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>155818</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>155818</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>258736</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>258736</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>258736</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>18817</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>12587</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>25533</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>28,57%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>19,11%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>38,77%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>15506</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>10570</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>21570</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>22,91%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>15,62%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>15305</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14729</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29400</t>
+          <t>22226</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>37428</t>
+          <t>34123</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28749</t>
+          <t>26410</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46981</t>
+          <t>43023</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>47046</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>40330</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>53276</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>71,43%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>61,23%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>80,89%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>52182</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>46118</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>57118</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>77,09%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>68,13%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>84,38%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>47110</t>
+          <t>54021</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39631</t>
+          <t>47100</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54302</t>
+          <t>58706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>99291</t>
+          <t>101067</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89738</t>
+          <t>92167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107970</t>
+          <t>108780</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>67688</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>67688</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>67688</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>69326</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>69326</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>69326</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>136719</t>
+          <t>135190</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>136719</t>
+          <t>135190</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>136719</t>
+          <t>135190</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>218279</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>197006</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>242694</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>32,49%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>29,32%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>36,12%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>284</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>217167</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>188435</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>276777</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>33,87%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>29,39%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>43,17%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>250599</t>
+          <t>181519</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>222381</t>
+          <t>162577</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>273832</t>
+          <t>200136</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>467767</t>
+          <t>399798</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>429548</t>
+          <t>368784</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>533742</t>
+          <t>429984</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>453581</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>429166</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>474854</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>67,51%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>63,88%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>70,68%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>611</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>424030</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>364420</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>452762</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>66,13%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>56,83%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>70,61%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>476588</t>
+          <t>425081</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>453355</t>
+          <t>406464</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>504806</t>
+          <t>444023</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>900617</t>
+          <t>878662</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>834642</t>
+          <t>848476</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>938836</t>
+          <t>909676</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>71,15%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>671860</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>671860</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>671860</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>895</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>641197</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>641197</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>641197</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>727187</t>
+          <t>606600</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>727187</t>
+          <t>606600</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>727187</t>
+          <t>606600</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1368384</t>
+          <t>1278460</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1368384</t>
+          <t>1278460</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1368384</t>
+          <t>1278460</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
